--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O632"/>
+  <dimension ref="A1:O638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32684,6 +32684,312 @@
         <v>382.03</v>
       </c>
       <c r="O632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>398.04</v>
+      </c>
+      <c r="C633" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="D633" t="n">
+        <v>375</v>
+      </c>
+      <c r="E633" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="F633" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="G633" t="n">
+        <v>385.09</v>
+      </c>
+      <c r="H633" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="I633" t="n">
+        <v>388.38</v>
+      </c>
+      <c r="J633" t="n">
+        <v>389</v>
+      </c>
+      <c r="K633" t="n">
+        <v>390.4</v>
+      </c>
+      <c r="L633" t="n">
+        <v>387.82</v>
+      </c>
+      <c r="M633" t="n">
+        <v>382.88</v>
+      </c>
+      <c r="N633" t="n">
+        <v>382.62</v>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>397.59</v>
+      </c>
+      <c r="C634" t="n">
+        <v>381.63</v>
+      </c>
+      <c r="D634" t="n">
+        <v>375.05</v>
+      </c>
+      <c r="E634" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="F634" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="G634" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="H634" t="n">
+        <v>385.71</v>
+      </c>
+      <c r="I634" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="J634" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="K634" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="L634" t="n">
+        <v>388.02</v>
+      </c>
+      <c r="M634" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="N634" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>398.54</v>
+      </c>
+      <c r="C635" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="D635" t="n">
+        <v>375.61</v>
+      </c>
+      <c r="E635" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="F635" t="n">
+        <v>382.29</v>
+      </c>
+      <c r="G635" t="n">
+        <v>385.43</v>
+      </c>
+      <c r="H635" t="n">
+        <v>386.37</v>
+      </c>
+      <c r="I635" t="n">
+        <v>388.95</v>
+      </c>
+      <c r="J635" t="n">
+        <v>389.25</v>
+      </c>
+      <c r="K635" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="L635" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="M635" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="N635" t="n">
+        <v>382.23</v>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>398.77</v>
+      </c>
+      <c r="C636" t="n">
+        <v>382.22</v>
+      </c>
+      <c r="D636" t="n">
+        <v>375.46</v>
+      </c>
+      <c r="E636" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="F636" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="G636" t="n">
+        <v>385.32</v>
+      </c>
+      <c r="H636" t="n">
+        <v>386.62</v>
+      </c>
+      <c r="I636" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="J636" t="n">
+        <v>389.17</v>
+      </c>
+      <c r="K636" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="L636" t="n">
+        <v>386.75</v>
+      </c>
+      <c r="M636" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="N636" t="n">
+        <v>381.38</v>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>398.91</v>
+      </c>
+      <c r="C637" t="n">
+        <v>382.17</v>
+      </c>
+      <c r="D637" t="n">
+        <v>375.46</v>
+      </c>
+      <c r="E637" t="n">
+        <v>369.62</v>
+      </c>
+      <c r="F637" t="n">
+        <v>381.86</v>
+      </c>
+      <c r="G637" t="n">
+        <v>385.33</v>
+      </c>
+      <c r="H637" t="n">
+        <v>386.62</v>
+      </c>
+      <c r="I637" t="n">
+        <v>389</v>
+      </c>
+      <c r="J637" t="n">
+        <v>389.21</v>
+      </c>
+      <c r="K637" t="n">
+        <v>390.19</v>
+      </c>
+      <c r="L637" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="M637" t="n">
+        <v>381.96</v>
+      </c>
+      <c r="N637" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>399.14</v>
+      </c>
+      <c r="C638" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="D638" t="n">
+        <v>375.28</v>
+      </c>
+      <c r="E638" t="n">
+        <v>369.44</v>
+      </c>
+      <c r="F638" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="G638" t="n">
+        <v>385.37</v>
+      </c>
+      <c r="H638" t="n">
+        <v>386.64</v>
+      </c>
+      <c r="I638" t="n">
+        <v>388.93</v>
+      </c>
+      <c r="J638" t="n">
+        <v>389.19</v>
+      </c>
+      <c r="K638" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="L638" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="M638" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="N638" t="n">
+        <v>381.63</v>
+      </c>
+      <c r="O638" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32700,7 +33006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B647"/>
+  <dimension ref="A1:B653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39173,6 +39479,66 @@
       </c>
       <c r="B647" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -39341,28 +39707,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2488629308012003</v>
+        <v>-0.2610041119101775</v>
       </c>
       <c r="J2" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K2" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07784138625918813</v>
+        <v>0.08576417734473551</v>
       </c>
       <c r="M2" t="n">
-        <v>5.18399567483924</v>
+        <v>5.199982239589175</v>
       </c>
       <c r="N2" t="n">
-        <v>40.51559830539987</v>
+        <v>40.53798814127938</v>
       </c>
       <c r="O2" t="n">
-        <v>6.365186431315258</v>
+        <v>6.366944961382923</v>
       </c>
       <c r="P2" t="n">
-        <v>411.8132524489489</v>
+        <v>411.9453187975714</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39419,28 +39785,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2381118015261721</v>
+        <v>-0.2451988612802916</v>
       </c>
       <c r="J3" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K3" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07146176339929511</v>
+        <v>0.07664057046887529</v>
       </c>
       <c r="M3" t="n">
-        <v>5.219089326061108</v>
+        <v>5.204415745658584</v>
       </c>
       <c r="N3" t="n">
-        <v>40.68128603210236</v>
+        <v>40.43562333038059</v>
       </c>
       <c r="O3" t="n">
-        <v>6.378188303280357</v>
+        <v>6.358901110284747</v>
       </c>
       <c r="P3" t="n">
-        <v>392.2352254597546</v>
+        <v>392.3123191698858</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39497,28 +39863,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2526094041877168</v>
+        <v>-0.2556379582374079</v>
       </c>
       <c r="J4" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K4" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1001688138640326</v>
+        <v>0.1041425637736734</v>
       </c>
       <c r="M4" t="n">
-        <v>4.599616039756229</v>
+        <v>4.572102378939222</v>
       </c>
       <c r="N4" t="n">
-        <v>31.65441608923604</v>
+        <v>31.38170264560209</v>
       </c>
       <c r="O4" t="n">
-        <v>5.626225741048438</v>
+        <v>5.601937401078496</v>
       </c>
       <c r="P4" t="n">
-        <v>383.7538422480238</v>
+        <v>383.7867858096258</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39575,28 +39941,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2265786782292212</v>
+        <v>-0.2296521223096605</v>
       </c>
       <c r="J5" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K5" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0931115890292924</v>
+        <v>0.09709441733915725</v>
       </c>
       <c r="M5" t="n">
-        <v>4.268659037323869</v>
+        <v>4.247562750413846</v>
       </c>
       <c r="N5" t="n">
-        <v>27.61181531308952</v>
+        <v>27.3781557238225</v>
       </c>
       <c r="O5" t="n">
-        <v>5.254694597508928</v>
+        <v>5.232413948057101</v>
       </c>
       <c r="P5" t="n">
-        <v>377.5947156105184</v>
+        <v>377.6281548039629</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39653,28 +40019,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2056669080993982</v>
+        <v>-0.2041885665602381</v>
       </c>
       <c r="J6" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K6" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07129855262044993</v>
+        <v>0.07167393270572076</v>
       </c>
       <c r="M6" t="n">
-        <v>4.334731413183802</v>
+        <v>4.299598952933323</v>
       </c>
       <c r="N6" t="n">
-        <v>30.42503000055117</v>
+        <v>30.14514214643702</v>
       </c>
       <c r="O6" t="n">
-        <v>5.515888867675923</v>
+        <v>5.490459192675693</v>
       </c>
       <c r="P6" t="n">
-        <v>386.8651255438494</v>
+        <v>386.8490488420254</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39731,28 +40097,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2530480477169068</v>
+        <v>-0.2535626320515432</v>
       </c>
       <c r="J7" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K7" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1079220038256939</v>
+        <v>0.1102876217874713</v>
       </c>
       <c r="M7" t="n">
-        <v>4.119771120470715</v>
+        <v>4.084287203310507</v>
       </c>
       <c r="N7" t="n">
-        <v>29.22843599813909</v>
+        <v>28.95399852065186</v>
       </c>
       <c r="O7" t="n">
-        <v>5.406332952948707</v>
+        <v>5.380891981879199</v>
       </c>
       <c r="P7" t="n">
-        <v>392.3664397561977</v>
+        <v>392.3720357199521</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39809,28 +40175,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2618035340260235</v>
+        <v>-0.260716639999758</v>
       </c>
       <c r="J8" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K8" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1293771319315855</v>
+        <v>0.130710600208234</v>
       </c>
       <c r="M8" t="n">
-        <v>3.830193019327973</v>
+        <v>3.798812325042244</v>
       </c>
       <c r="N8" t="n">
-        <v>25.47008113785877</v>
+        <v>25.2351714897424</v>
       </c>
       <c r="O8" t="n">
-        <v>5.04678919094693</v>
+        <v>5.023462101951441</v>
       </c>
       <c r="P8" t="n">
-        <v>392.7107884267554</v>
+        <v>392.69895716696</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39887,28 +40253,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1265521501129862</v>
+        <v>-0.1271409132555468</v>
       </c>
       <c r="J9" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K9" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04188667999679607</v>
+        <v>0.04308722107065932</v>
       </c>
       <c r="M9" t="n">
-        <v>3.407472250979841</v>
+        <v>3.378146845546637</v>
       </c>
       <c r="N9" t="n">
-        <v>20.22957521929251</v>
+        <v>20.04055326866525</v>
       </c>
       <c r="O9" t="n">
-        <v>4.497730007380668</v>
+        <v>4.476667652245949</v>
       </c>
       <c r="P9" t="n">
-        <v>392.5238774883636</v>
+        <v>392.5302785182907</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39965,28 +40331,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0718564695581189</v>
+        <v>-0.07573454038821924</v>
       </c>
       <c r="J10" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K10" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0189414871176059</v>
+        <v>0.02136000962630136</v>
       </c>
       <c r="M10" t="n">
-        <v>2.985040337601669</v>
+        <v>2.972677431206644</v>
       </c>
       <c r="N10" t="n">
-        <v>14.76792088808547</v>
+        <v>14.66981669285828</v>
       </c>
       <c r="O10" t="n">
-        <v>3.842905266603052</v>
+        <v>3.830119670827307</v>
       </c>
       <c r="P10" t="n">
-        <v>393.2021178913475</v>
+        <v>393.2443038866003</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40043,28 +40409,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05216239517804312</v>
+        <v>0.04793642381781185</v>
       </c>
       <c r="J11" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K11" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008729035253426831</v>
+        <v>0.007510637440531154</v>
       </c>
       <c r="M11" t="n">
-        <v>3.226435185900079</v>
+        <v>3.215100403978412</v>
       </c>
       <c r="N11" t="n">
-        <v>17.06270790247819</v>
+        <v>16.95100726931177</v>
       </c>
       <c r="O11" t="n">
-        <v>4.130703076048699</v>
+        <v>4.117160097605116</v>
       </c>
       <c r="P11" t="n">
-        <v>391.1849374225008</v>
+        <v>391.2309125954654</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40121,28 +40487,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0827375469575478</v>
+        <v>-0.08453528392129979</v>
       </c>
       <c r="J12" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K12" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02258090169814175</v>
+        <v>0.0240044423634953</v>
       </c>
       <c r="M12" t="n">
-        <v>3.191717228900505</v>
+        <v>3.168580479022072</v>
       </c>
       <c r="N12" t="n">
-        <v>16.3625727251051</v>
+        <v>16.21987246651332</v>
       </c>
       <c r="O12" t="n">
-        <v>4.045067703401898</v>
+        <v>4.027390279885141</v>
       </c>
       <c r="P12" t="n">
-        <v>390.4579861952536</v>
+        <v>390.4775519959205</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40199,28 +40565,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1120471461031842</v>
+        <v>-0.1198348193239408</v>
       </c>
       <c r="J13" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K13" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04563424616218215</v>
+        <v>0.05228474861962662</v>
       </c>
       <c r="M13" t="n">
-        <v>3.001060052293236</v>
+        <v>3.005073967155655</v>
       </c>
       <c r="N13" t="n">
-        <v>14.4988091377896</v>
+        <v>14.5306178353574</v>
       </c>
       <c r="O13" t="n">
-        <v>3.807730181852386</v>
+        <v>3.811904751611378</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5743005033552</v>
+        <v>389.6590279707407</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -40277,28 +40643,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1400459229197512</v>
+        <v>-0.1545315002743837</v>
       </c>
       <c r="J14" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K14" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03878245650128642</v>
+        <v>0.04677861609168665</v>
       </c>
       <c r="M14" t="n">
-        <v>4.164872187292342</v>
+        <v>4.177921381490131</v>
       </c>
       <c r="N14" t="n">
-        <v>26.84318735829758</v>
+        <v>27.16411957100843</v>
       </c>
       <c r="O14" t="n">
-        <v>5.181041146169134</v>
+        <v>5.211920909895739</v>
       </c>
       <c r="P14" t="n">
-        <v>393.7707415146275</v>
+        <v>393.9283295135425</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -40336,7 +40702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O632"/>
+  <dimension ref="A1:O638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89003,6 +89369,468 @@
         </is>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-36.67997799137996,174.7490711388863</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-36.68068754773448,174.749363583305</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-36.68138749844849,174.74964548773218</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-36.682078809731046,174.74994266384329</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-36.68276332997477,174.75024767686477</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-36.68343523543432,174.75050916411013</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>-36.684110149044876,174.75080017738046</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>-36.68478434527336,174.7511170627109</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>-36.6854648937269,174.75141145998737</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>-36.686132599137636,174.75170908968096</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>-36.68678882047845,174.75203264922456</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>-36.687456805766914,174.75236303303458</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>-36.68810975611671,174.75274255581996</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-36.67998003986556,174.74906679342027</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-36.680687466662135,174.74936378317003</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-36.68138732142775,174.7496460022083</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-36.682078648868334,174.74994330479848</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-36.68276352346777,174.7502466989044</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-36.68343507066066,174.75050980354314</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>-36.68410991023546,174.7508010220062</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>-36.684783837799856,174.7511188575545</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>-36.68546456535966,174.75141262136597</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>-36.68613176517453,174.75171168842556</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>-36.68678805970769,174.7520346780773</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>-36.68745535322771,174.7523667598523</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>-36.68810842134355,174.75274598048713</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-36.67997571528465,174.74907596718165</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-36.68068454805743,174.74937097831017</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-36.681385338795494,174.74965176434057</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-36.68207891697287,174.74994223653982</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-36.68276382445686,174.75024517763265</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>-36.68343430171681,174.75051278756385</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>-36.68410794005756,174.7508079901683</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>-36.68478264374444,174.75112308071576</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>-36.68546414743767,174.75141409948415</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>-36.686132699213196,174.75170877783162</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>-36.68679030398134,174.7520286929616</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>-36.68745845459507,174.75235880259274</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>-36.68811128717994,174.75273862752513</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-36.67997466828075,174.7490781881974</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-36.68068507502776,174.7493696791877</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-36.68138586985773,174.74965022091232</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-36.68208015025363,174.74993732255</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-36.68276457692952,174.75024137445325</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-36.6834346038019,174.75051161527</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>-36.68410719377794,174.75081062962357</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>-36.684782464636115,174.75112371418996</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>-36.68546438625024,174.75141325484518</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>-36.68613373332737,174.75170555538824</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>-36.68679289060148,174.7520217948617</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>-36.68746155596192,174.7523508453325</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>-36.68811462411216,174.7527300658563</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-36.679974030974,174.74907954012</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-36.68068527770865,174.7493691795252</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-36.68138586985773,174.74965022091232</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-36.68208009663273,174.74993753620174</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-36.68276474892326,174.7502405051551</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-36.683434576339614,174.75051172184217</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-36.68410719377794,174.75081062962357</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>-36.684782494487486,174.75112360861092</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>-36.685464266843965,174.75141367716466</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>-36.686133299666594,174.75170690673548</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>-36.68679270040883,174.75202230207492</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>-36.68746041748554,174.75235376635217</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>-36.68811289675908,174.7527344977791</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.679972983970025,174.74908176113564</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.68068669647482,174.7493656818876</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.681386507132395,174.74964836879838</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.68208057922081,174.74993561333613</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-36.68276485641935,174.75023996184376</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-36.683434466490496,174.75051214813084</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-36.684107134075575,174.75081084078</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>-36.684782703447205,174.75112286955772</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>-36.685464326547105,174.75141346600492</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>-36.686133800044416,174.75170534748867</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>-36.68679304275559,174.75202138909106</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>-36.68746155596192,174.7523508453325</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>-36.68811364266157,174.7527325839943</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
